--- a/datos/repositorio prueba trimestral.xlsx
+++ b/datos/repositorio prueba trimestral.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2289D6F0-86D3-4761-8D4B-9186EF027717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8313660C-B41D-4C63-8E1A-5F521DBB75CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF28ABC6-9E45-43EC-AA8F-B480BA3DE30B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="33">
   <si>
     <t>CEDI</t>
   </si>
@@ -132,6 +132,12 @@
   </si>
   <si>
     <t>TOALOMBO LLACA ROSA ISABEL</t>
+  </si>
+  <si>
+    <t>MARCA</t>
+  </si>
+  <si>
+    <t>SUBCATEGORIA</t>
   </si>
 </sst>
 </file>
@@ -630,18 +636,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3898A9C6-98A7-4AA3-8BAF-4B75AC1084B9}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" customWidth="1"/>
     <col min="3" max="3" width="22.44140625" customWidth="1"/>
-    <col min="5" max="5" width="41.21875" customWidth="1"/>
-    <col min="7" max="7" width="31.88671875" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.88671875" customWidth="1"/>
+    <col min="7" max="7" width="41.21875" customWidth="1"/>
+    <col min="9" max="9" width="31.88671875" customWidth="1"/>
+    <col min="10" max="10" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -655,19 +663,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -680,21 +694,23 @@
       <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="7" t="str">
-        <f t="shared" ref="E2:E61" si="0">_xlfn.CONCAT(B2,D2)</f>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="str">
+        <f>_xlfn.CONCAT(B2,D2)</f>
         <v>ZAMBRANO ZAMBRANO CLEYTON ELIECERBARRA</v>
-      </c>
-      <c r="F2" s="8">
-        <v>600</v>
-      </c>
-      <c r="G2" s="8">
-        <v>600</v>
       </c>
       <c r="H2" s="8">
         <v>600</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="8">
+        <v>600</v>
+      </c>
+      <c r="J2" s="8">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -707,21 +723,23 @@
       <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="str">
+        <f>_xlfn.CONCAT(B3,D3)</f>
         <v>ZAMBRANO ZAMBRANO CLEYTON ELIECERCREMA</v>
-      </c>
-      <c r="F3" s="8">
-        <v>1314</v>
-      </c>
-      <c r="G3" s="8">
-        <v>1314</v>
       </c>
       <c r="H3" s="8">
         <v>1314</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="8">
+        <v>1314</v>
+      </c>
+      <c r="J3" s="8">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -734,20 +752,22 @@
       <c r="D4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="F4" s="8">
-        <v>110</v>
-      </c>
-      <c r="G4" s="8">
-        <v>110</v>
       </c>
       <c r="H4" s="8">
         <v>110</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="8">
+        <v>110</v>
+      </c>
+      <c r="J4" s="8">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -760,21 +780,23 @@
       <c r="D5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7" t="str">
+        <f>_xlfn.CONCAT(B5,D5)</f>
         <v>ZAMBRANO ZAMBRANO CLEYTON ELIECERPOLVO DETERGENTE</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1650</v>
-      </c>
-      <c r="G5" s="8">
-        <v>1650</v>
       </c>
       <c r="H5" s="8">
         <v>1650</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="8">
+        <v>1650</v>
+      </c>
+      <c r="J5" s="8">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -787,21 +809,23 @@
       <c r="D6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="str">
+        <f>_xlfn.CONCAT(B6,D6)</f>
         <v>ZAMBRANO ZAMBRANO CLEYTON ELIECEROTRAS CATEGORIAS</v>
       </c>
-      <c r="F6" s="8">
-        <v>10</v>
-      </c>
-      <c r="G6" s="8">
-        <v>10</v>
-      </c>
       <c r="H6" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="8">
+        <v>10</v>
+      </c>
+      <c r="J6" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -814,21 +838,23 @@
       <c r="D7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="str">
+        <f>_xlfn.CONCAT(B7,D7)</f>
         <v>ZAMBRANO VALENCIA MARGARITABARRA</v>
-      </c>
-      <c r="F7" s="8">
-        <v>2152.88</v>
-      </c>
-      <c r="G7" s="8">
-        <v>2152.88</v>
       </c>
       <c r="H7" s="8">
         <v>2152.88</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="8">
+        <v>2152.88</v>
+      </c>
+      <c r="J7" s="8">
+        <v>2152.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -841,21 +867,23 @@
       <c r="D8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="str">
+        <f>_xlfn.CONCAT(B8,D8)</f>
         <v>ZAMBRANO VALENCIA MARGARITACREMA</v>
-      </c>
-      <c r="F8" s="8">
-        <v>2051</v>
-      </c>
-      <c r="G8" s="8">
-        <v>2051</v>
       </c>
       <c r="H8" s="8">
         <v>2051</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="8">
+        <v>2051</v>
+      </c>
+      <c r="J8" s="8">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
@@ -868,21 +896,23 @@
       <c r="D9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="str">
+        <f>_xlfn.CONCAT(B9,D9)</f>
         <v>ZAMBRANO VALENCIA MARGARITALIQUIDO</v>
-      </c>
-      <c r="F9" s="8">
-        <v>643</v>
-      </c>
-      <c r="G9" s="8">
-        <v>643</v>
       </c>
       <c r="H9" s="8">
         <v>643</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="8">
+        <v>643</v>
+      </c>
+      <c r="J9" s="8">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
@@ -895,21 +925,23 @@
       <c r="D10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="str">
+        <f>_xlfn.CONCAT(B10,D10)</f>
         <v>ZAMBRANO VALENCIA MARGARITAPOLVO DETERGENTE</v>
-      </c>
-      <c r="F10" s="8">
-        <v>3480</v>
-      </c>
-      <c r="G10" s="8">
-        <v>3480</v>
       </c>
       <c r="H10" s="8">
         <v>3480</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="8">
+        <v>3480</v>
+      </c>
+      <c r="J10" s="8">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
@@ -922,21 +954,23 @@
       <c r="D11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7" t="str">
+        <f>_xlfn.CONCAT(B11,D11)</f>
         <v>ZAMBRANO VALENCIA MARGARITAOTRAS CATEGORIAS</v>
-      </c>
-      <c r="F11" s="8">
-        <v>30</v>
-      </c>
-      <c r="G11" s="8">
-        <v>30</v>
       </c>
       <c r="H11" s="8">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="8">
+        <v>30</v>
+      </c>
+      <c r="J11" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>8</v>
       </c>
@@ -949,21 +983,23 @@
       <c r="D12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="str">
+        <f>_xlfn.CONCAT(B12,D12)</f>
         <v>ZAMBRANO MOLINA JORGE EDUARDOBARRA</v>
-      </c>
-      <c r="F12" s="8">
-        <v>556</v>
-      </c>
-      <c r="G12" s="8">
-        <v>556</v>
       </c>
       <c r="H12" s="8">
         <v>556</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="8">
+        <v>556</v>
+      </c>
+      <c r="J12" s="8">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
@@ -976,21 +1012,23 @@
       <c r="D13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="str">
+        <f>_xlfn.CONCAT(B13,D13)</f>
         <v>ZAMBRANO MOLINA JORGE EDUARDOCREMA</v>
-      </c>
-      <c r="F13" s="8">
-        <v>1315.43</v>
-      </c>
-      <c r="G13" s="8">
-        <v>1315.43</v>
       </c>
       <c r="H13" s="8">
         <v>1315.43</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="8">
+        <v>1315.43</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1315.43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>8</v>
       </c>
@@ -1003,21 +1041,23 @@
       <c r="D14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7" t="str">
+        <f>_xlfn.CONCAT(B14,D14)</f>
         <v>ZAMBRANO MOLINA JORGE EDUARDOLIQUIDO</v>
-      </c>
-      <c r="F14" s="8">
-        <v>430</v>
-      </c>
-      <c r="G14" s="8">
-        <v>430</v>
       </c>
       <c r="H14" s="8">
         <v>430</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" s="8">
+        <v>430</v>
+      </c>
+      <c r="J14" s="8">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>8</v>
       </c>
@@ -1030,21 +1070,23 @@
       <c r="D15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7" t="str">
+        <f>_xlfn.CONCAT(B15,D15)</f>
         <v>ZAMBRANO MOLINA JORGE EDUARDOPOLVO DETERGENTE</v>
-      </c>
-      <c r="F15" s="8">
-        <v>1112</v>
-      </c>
-      <c r="G15" s="8">
-        <v>1112</v>
       </c>
       <c r="H15" s="8">
         <v>1112</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" s="8">
+        <v>1112</v>
+      </c>
+      <c r="J15" s="8">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
@@ -1057,21 +1099,23 @@
       <c r="D16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7" t="str">
+        <f>_xlfn.CONCAT(B16,D16)</f>
         <v>ZAMBRANO MOLINA JORGE EDUARDOOTRAS CATEGORIAS</v>
       </c>
-      <c r="F16" s="8">
-        <v>10</v>
-      </c>
-      <c r="G16" s="8">
-        <v>10</v>
-      </c>
       <c r="H16" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="8">
+        <v>10</v>
+      </c>
+      <c r="J16" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>8</v>
       </c>
@@ -1084,21 +1128,23 @@
       <c r="D17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7" t="str">
+        <f>_xlfn.CONCAT(B17,D17)</f>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOBARRA</v>
-      </c>
-      <c r="F17" s="8">
-        <v>1500</v>
-      </c>
-      <c r="G17" s="8">
-        <v>1500</v>
       </c>
       <c r="H17" s="8">
         <v>1500</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="8">
+        <v>1500</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>8</v>
       </c>
@@ -1111,21 +1157,23 @@
       <c r="D18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7" t="str">
+        <f>_xlfn.CONCAT(B18,D18)</f>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOCREMA</v>
-      </c>
-      <c r="F18" s="8">
-        <v>2497.64</v>
-      </c>
-      <c r="G18" s="8">
-        <v>2497.64</v>
       </c>
       <c r="H18" s="8">
         <v>2497.64</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="8">
+        <v>2497.64</v>
+      </c>
+      <c r="J18" s="8">
+        <v>2497.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>8</v>
       </c>
@@ -1138,21 +1186,23 @@
       <c r="D19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="str">
+        <f>_xlfn.CONCAT(B19,D19)</f>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOLIQUIDO</v>
-      </c>
-      <c r="F19" s="8">
-        <v>442</v>
-      </c>
-      <c r="G19" s="8">
-        <v>442</v>
       </c>
       <c r="H19" s="8">
         <v>442</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="8">
+        <v>442</v>
+      </c>
+      <c r="J19" s="8">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>8</v>
       </c>
@@ -1165,21 +1215,23 @@
       <c r="D20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7" t="str">
+        <f>_xlfn.CONCAT(B20,D20)</f>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOPOLVO DETERGENTE</v>
-      </c>
-      <c r="F20" s="8">
-        <v>4700</v>
-      </c>
-      <c r="G20" s="8">
-        <v>4700</v>
       </c>
       <c r="H20" s="8">
         <v>4700</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="8">
+        <v>4700</v>
+      </c>
+      <c r="J20" s="8">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>8</v>
       </c>
@@ -1192,21 +1244,23 @@
       <c r="D21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7" t="str">
+        <f>_xlfn.CONCAT(B21,D21)</f>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOOTRAS CATEGORIAS</v>
-      </c>
-      <c r="F21" s="8">
-        <v>20</v>
-      </c>
-      <c r="G21" s="8">
-        <v>20</v>
       </c>
       <c r="H21" s="8">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="8">
+        <v>20</v>
+      </c>
+      <c r="J21" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
@@ -1219,21 +1273,23 @@
       <c r="D22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7" t="str">
+        <f>_xlfn.CONCAT(B22,D22)</f>
         <v>YUCAILLA PADILLA RENE WILFRIDOBARRA</v>
-      </c>
-      <c r="F22" s="9">
-        <v>15</v>
-      </c>
-      <c r="G22" s="9">
-        <v>15</v>
       </c>
       <c r="H22" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="9">
+        <v>15</v>
+      </c>
+      <c r="J22" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>20</v>
       </c>
@@ -1246,21 +1302,23 @@
       <c r="D23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7" t="str">
+        <f>_xlfn.CONCAT(B23,D23)</f>
         <v>YUCAILLA PADILLA RENE WILFRIDOCREMA</v>
-      </c>
-      <c r="F23" s="8">
-        <v>1611</v>
-      </c>
-      <c r="G23" s="8">
-        <v>1611</v>
       </c>
       <c r="H23" s="8">
         <v>1611</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="8">
+        <v>1611</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>20</v>
       </c>
@@ -1273,21 +1331,23 @@
       <c r="D24" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7" t="str">
+        <f>_xlfn.CONCAT(B24,D24)</f>
         <v>YUCAILLA PADILLA RENE WILFRIDOLIQUIDO</v>
-      </c>
-      <c r="F24" s="8">
-        <v>15</v>
-      </c>
-      <c r="G24" s="8">
-        <v>15</v>
       </c>
       <c r="H24" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24" s="8">
+        <v>15</v>
+      </c>
+      <c r="J24" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
@@ -1300,21 +1360,23 @@
       <c r="D25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="str">
+        <f>_xlfn.CONCAT(B25,D25)</f>
         <v>YUCAILLA PADILLA RENE WILFRIDOPOLVO DETERGENTE</v>
-      </c>
-      <c r="F25" s="9">
-        <v>427</v>
-      </c>
-      <c r="G25" s="9">
-        <v>427</v>
       </c>
       <c r="H25" s="9">
         <v>427</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25" s="9">
+        <v>427</v>
+      </c>
+      <c r="J25" s="9">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>20</v>
       </c>
@@ -1327,15 +1389,17 @@
       <c r="D26" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7" t="str">
+        <f>_xlfn.CONCAT(B26,D26)</f>
         <v>YUCAILLA PADILLA RENE WILFRIDOOTRAS CATEGORIAS</v>
       </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
@@ -1348,21 +1412,23 @@
       <c r="D27" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7" t="str">
+        <f>_xlfn.CONCAT(B27,D27)</f>
         <v>YANEZ CARDENAS ESTELA ELIZABETHBARRA</v>
-      </c>
-      <c r="F27" s="8">
-        <v>3585</v>
-      </c>
-      <c r="G27" s="8">
-        <v>3585</v>
       </c>
       <c r="H27" s="8">
         <v>3585</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27" s="8">
+        <v>3585</v>
+      </c>
+      <c r="J27" s="8">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>22</v>
       </c>
@@ -1375,21 +1441,23 @@
       <c r="D28" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E28" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7" t="str">
+        <f>_xlfn.CONCAT(B28,D28)</f>
         <v>YANEZ CARDENAS ESTELA ELIZABETHCREMA</v>
-      </c>
-      <c r="F28" s="8">
-        <v>637</v>
-      </c>
-      <c r="G28" s="8">
-        <v>637</v>
       </c>
       <c r="H28" s="8">
         <v>637</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28" s="8">
+        <v>637</v>
+      </c>
+      <c r="J28" s="8">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>22</v>
       </c>
@@ -1402,21 +1470,23 @@
       <c r="D29" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7" t="str">
+        <f>_xlfn.CONCAT(B29,D29)</f>
         <v>YANEZ CARDENAS ESTELA ELIZABETHLIQUIDO</v>
-      </c>
-      <c r="F29" s="8">
-        <v>500</v>
-      </c>
-      <c r="G29" s="8">
-        <v>500</v>
       </c>
       <c r="H29" s="8">
         <v>500</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29" s="8">
+        <v>500</v>
+      </c>
+      <c r="J29" s="8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>22</v>
       </c>
@@ -1429,21 +1499,23 @@
       <c r="D30" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7" t="str">
+        <f>_xlfn.CONCAT(B30,D30)</f>
         <v>YANEZ CARDENAS ESTELA ELIZABETHPOLVO DETERGENTE</v>
-      </c>
-      <c r="F30" s="8">
-        <v>5493</v>
-      </c>
-      <c r="G30" s="8">
-        <v>5493</v>
       </c>
       <c r="H30" s="8">
         <v>5493</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="8">
+        <v>5493</v>
+      </c>
+      <c r="J30" s="8">
+        <v>5493</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>22</v>
       </c>
@@ -1456,21 +1528,23 @@
       <c r="D31" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7" t="str">
+        <f>_xlfn.CONCAT(B31,D31)</f>
         <v>YANEZ CARDENAS ESTELA ELIZABETHOTRAS CATEGORIAS</v>
-      </c>
-      <c r="F31" s="8">
-        <v>60</v>
-      </c>
-      <c r="G31" s="8">
-        <v>60</v>
       </c>
       <c r="H31" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31" s="8">
+        <v>60</v>
+      </c>
+      <c r="J31" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
@@ -1483,21 +1557,23 @@
       <c r="D32" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7" t="str">
+        <f>_xlfn.CONCAT(B32,D32)</f>
         <v>YAGUACHI QUISHPI MARIA ELVIRABARRA</v>
-      </c>
-      <c r="F32" s="8">
-        <v>4600</v>
-      </c>
-      <c r="G32" s="8">
-        <v>4600</v>
       </c>
       <c r="H32" s="8">
         <v>4600</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I32" s="8">
+        <v>4600</v>
+      </c>
+      <c r="J32" s="8">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>22</v>
       </c>
@@ -1510,21 +1586,23 @@
       <c r="D33" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E33" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7" t="str">
+        <f>_xlfn.CONCAT(B33,D33)</f>
         <v>YAGUACHI QUISHPI MARIA ELVIRACREMA</v>
-      </c>
-      <c r="F33" s="8">
-        <v>1025</v>
-      </c>
-      <c r="G33" s="8">
-        <v>1025</v>
       </c>
       <c r="H33" s="8">
         <v>1025</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I33" s="8">
+        <v>1025</v>
+      </c>
+      <c r="J33" s="8">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>22</v>
       </c>
@@ -1537,21 +1615,23 @@
       <c r="D34" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7" t="str">
+        <f>_xlfn.CONCAT(B34,D34)</f>
         <v>YAGUACHI QUISHPI MARIA ELVIRALIQUIDO</v>
-      </c>
-      <c r="F34" s="8">
-        <v>250</v>
-      </c>
-      <c r="G34" s="8">
-        <v>250</v>
       </c>
       <c r="H34" s="8">
         <v>250</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I34" s="8">
+        <v>250</v>
+      </c>
+      <c r="J34" s="8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>22</v>
       </c>
@@ -1564,21 +1644,23 @@
       <c r="D35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7" t="str">
+        <f>_xlfn.CONCAT(B35,D35)</f>
         <v>YAGUACHI QUISHPI MARIA ELVIRAPOLVO DETERGENTE</v>
-      </c>
-      <c r="F35" s="8">
-        <v>6400</v>
-      </c>
-      <c r="G35" s="8">
-        <v>6400</v>
       </c>
       <c r="H35" s="8">
         <v>6400</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I35" s="8">
+        <v>6400</v>
+      </c>
+      <c r="J35" s="8">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>22</v>
       </c>
@@ -1591,21 +1673,23 @@
       <c r="D36" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7" t="str">
+        <f>_xlfn.CONCAT(B36,D36)</f>
         <v>YAGUACHI QUISHPI MARIA ELVIRAOTRAS CATEGORIAS</v>
-      </c>
-      <c r="F36" s="8">
-        <v>60</v>
-      </c>
-      <c r="G36" s="8">
-        <v>60</v>
       </c>
       <c r="H36" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I36" s="8">
+        <v>60</v>
+      </c>
+      <c r="J36" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>8</v>
       </c>
@@ -1618,21 +1702,23 @@
       <c r="D37" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7" t="str">
+        <f>_xlfn.CONCAT(B37,D37)</f>
         <v>WANG CHONG LONGBARRA</v>
-      </c>
-      <c r="F37" s="8">
-        <v>953.36</v>
-      </c>
-      <c r="G37" s="8">
-        <v>953.36</v>
       </c>
       <c r="H37" s="8">
         <v>953.36</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I37" s="8">
+        <v>953.36</v>
+      </c>
+      <c r="J37" s="8">
+        <v>953.36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>8</v>
       </c>
@@ -1645,21 +1731,23 @@
       <c r="D38" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7" t="str">
+        <f>_xlfn.CONCAT(B38,D38)</f>
         <v>WANG CHONG LONGCREMA</v>
-      </c>
-      <c r="F38" s="8">
-        <v>1632.3400000000001</v>
-      </c>
-      <c r="G38" s="8">
-        <v>1632.3400000000001</v>
       </c>
       <c r="H38" s="8">
         <v>1632.3400000000001</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I38" s="8">
+        <v>1632.3400000000001</v>
+      </c>
+      <c r="J38" s="8">
+        <v>1632.3400000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>8</v>
       </c>
@@ -1672,21 +1760,23 @@
       <c r="D39" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7" t="str">
+        <f>_xlfn.CONCAT(B39,D39)</f>
         <v>WANG CHONG LONGLIQUIDO</v>
-      </c>
-      <c r="F39" s="8">
-        <v>374</v>
-      </c>
-      <c r="G39" s="8">
-        <v>374</v>
       </c>
       <c r="H39" s="8">
         <v>374</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I39" s="8">
+        <v>374</v>
+      </c>
+      <c r="J39" s="8">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>8</v>
       </c>
@@ -1699,21 +1789,23 @@
       <c r="D40" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E40" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7" t="str">
+        <f>_xlfn.CONCAT(B40,D40)</f>
         <v>WANG CHONG LONGPOLVO DETERGENTE</v>
-      </c>
-      <c r="F40" s="8">
-        <v>1764.9399999999998</v>
-      </c>
-      <c r="G40" s="8">
-        <v>1764.9399999999998</v>
       </c>
       <c r="H40" s="8">
         <v>1764.9399999999998</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I40" s="8">
+        <v>1764.9399999999998</v>
+      </c>
+      <c r="J40" s="8">
+        <v>1764.9399999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>8</v>
       </c>
@@ -1726,21 +1818,23 @@
       <c r="D41" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7" t="str">
+        <f>_xlfn.CONCAT(B41,D41)</f>
         <v>WANG CHONG LONGOTRAS CATEGORIAS</v>
-      </c>
-      <c r="F41" s="8">
-        <v>20</v>
-      </c>
-      <c r="G41" s="8">
-        <v>20</v>
       </c>
       <c r="H41" s="8">
         <v>20</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I41" s="8">
+        <v>20</v>
+      </c>
+      <c r="J41" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>8</v>
       </c>
@@ -1753,21 +1847,23 @@
       <c r="D42" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7" t="str">
+        <f>_xlfn.CONCAT(B42,D42)</f>
         <v>URETA MENDOZA YIMMY ANTONIOBARRA</v>
-      </c>
-      <c r="F42" s="8">
-        <v>1450</v>
-      </c>
-      <c r="G42" s="8">
-        <v>1450</v>
       </c>
       <c r="H42" s="8">
         <v>1450</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I42" s="8">
+        <v>1450</v>
+      </c>
+      <c r="J42" s="8">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>8</v>
       </c>
@@ -1780,21 +1876,23 @@
       <c r="D43" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7" t="str">
+        <f>_xlfn.CONCAT(B43,D43)</f>
         <v>URETA MENDOZA YIMMY ANTONIOCREMA</v>
-      </c>
-      <c r="F43" s="8">
-        <v>3000</v>
-      </c>
-      <c r="G43" s="8">
-        <v>3000</v>
       </c>
       <c r="H43" s="8">
         <v>3000</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I43" s="8">
+        <v>3000</v>
+      </c>
+      <c r="J43" s="8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>8</v>
       </c>
@@ -1807,21 +1905,23 @@
       <c r="D44" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7" t="str">
+        <f>_xlfn.CONCAT(B44,D44)</f>
         <v>URETA MENDOZA YIMMY ANTONIOLIQUIDO</v>
-      </c>
-      <c r="F44" s="8">
-        <v>466</v>
-      </c>
-      <c r="G44" s="8">
-        <v>466</v>
       </c>
       <c r="H44" s="8">
         <v>466</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I44" s="8">
+        <v>466</v>
+      </c>
+      <c r="J44" s="8">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>8</v>
       </c>
@@ -1834,21 +1934,23 @@
       <c r="D45" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E45" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7" t="str">
+        <f>_xlfn.CONCAT(B45,D45)</f>
         <v>URETA MENDOZA YIMMY ANTONIOPOLVO DETERGENTE</v>
-      </c>
-      <c r="F45" s="8">
-        <v>3000</v>
-      </c>
-      <c r="G45" s="8">
-        <v>3000</v>
       </c>
       <c r="H45" s="8">
         <v>3000</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I45" s="8">
+        <v>3000</v>
+      </c>
+      <c r="J45" s="8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>8</v>
       </c>
@@ -1861,21 +1963,23 @@
       <c r="D46" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E46" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7" t="str">
+        <f>_xlfn.CONCAT(B46,D46)</f>
         <v>URETA MENDOZA YIMMY ANTONIOOTRAS CATEGORIAS</v>
-      </c>
-      <c r="F46" s="8">
-        <v>15</v>
-      </c>
-      <c r="G46" s="8">
-        <v>15</v>
       </c>
       <c r="H46" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I46" s="8">
+        <v>15</v>
+      </c>
+      <c r="J46" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>8</v>
       </c>
@@ -1888,21 +1992,23 @@
       <c r="D47" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7" t="str">
+        <f>_xlfn.CONCAT(B47,D47)</f>
         <v>ROBERT - PONCE COMPANY S.A.SBARRA</v>
-      </c>
-      <c r="F47" s="8">
-        <v>855.1</v>
-      </c>
-      <c r="G47" s="8">
-        <v>855.1</v>
       </c>
       <c r="H47" s="8">
         <v>855.1</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I47" s="8">
+        <v>855.1</v>
+      </c>
+      <c r="J47" s="8">
+        <v>855.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>8</v>
       </c>
@@ -1915,21 +2021,23 @@
       <c r="D48" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E48" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7" t="str">
+        <f>_xlfn.CONCAT(B48,D48)</f>
         <v>ROBERT - PONCE COMPANY S.A.SCREMA</v>
-      </c>
-      <c r="F48" s="8">
-        <v>1300</v>
-      </c>
-      <c r="G48" s="8">
-        <v>1300</v>
       </c>
       <c r="H48" s="8">
         <v>1300</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I48" s="8">
+        <v>1300</v>
+      </c>
+      <c r="J48" s="8">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>8</v>
       </c>
@@ -1942,21 +2050,23 @@
       <c r="D49" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E49" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7" t="str">
+        <f>_xlfn.CONCAT(B49,D49)</f>
         <v>ROBERT - PONCE COMPANY S.A.SLIQUIDO</v>
-      </c>
-      <c r="F49" s="8">
-        <v>400</v>
-      </c>
-      <c r="G49" s="8">
-        <v>400</v>
       </c>
       <c r="H49" s="8">
         <v>400</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49" s="8">
+        <v>400</v>
+      </c>
+      <c r="J49" s="8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>8</v>
       </c>
@@ -1969,21 +2079,23 @@
       <c r="D50" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E50" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7" t="str">
+        <f>_xlfn.CONCAT(B50,D50)</f>
         <v>ROBERT - PONCE COMPANY S.A.SPOLVO DETERGENTE</v>
-      </c>
-      <c r="F50" s="8">
-        <v>1200</v>
-      </c>
-      <c r="G50" s="8">
-        <v>1200</v>
       </c>
       <c r="H50" s="8">
         <v>1200</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I50" s="8">
+        <v>1200</v>
+      </c>
+      <c r="J50" s="8">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>8</v>
       </c>
@@ -1996,21 +2108,23 @@
       <c r="D51" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E51" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7" t="str">
+        <f>_xlfn.CONCAT(B51,D51)</f>
         <v>ROBERT - PONCE COMPANY S.A.SOTRAS CATEGORIAS</v>
       </c>
-      <c r="F51" s="8">
-        <v>10</v>
-      </c>
-      <c r="G51" s="8">
-        <v>10</v>
-      </c>
       <c r="H51" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I51" s="8">
+        <v>10</v>
+      </c>
+      <c r="J51" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>8</v>
       </c>
@@ -2023,21 +2137,23 @@
       <c r="D52" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E52" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="7" t="str">
+        <f>_xlfn.CONCAT(B52,D52)</f>
         <v>URETA MENDOZA ERMEL RUBENBARRA</v>
-      </c>
-      <c r="F52" s="8">
-        <v>488.92</v>
-      </c>
-      <c r="G52" s="8">
-        <v>488.92</v>
       </c>
       <c r="H52" s="8">
         <v>488.92</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I52" s="8">
+        <v>488.92</v>
+      </c>
+      <c r="J52" s="8">
+        <v>488.92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>8</v>
       </c>
@@ -2050,21 +2166,23 @@
       <c r="D53" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E53" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="7" t="str">
+        <f>_xlfn.CONCAT(B53,D53)</f>
         <v>URETA MENDOZA ERMEL RUBENCREMA</v>
-      </c>
-      <c r="F53" s="8">
-        <v>535.16</v>
-      </c>
-      <c r="G53" s="8">
-        <v>535.16</v>
       </c>
       <c r="H53" s="8">
         <v>535.16</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I53" s="8">
+        <v>535.16</v>
+      </c>
+      <c r="J53" s="8">
+        <v>535.16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>8</v>
       </c>
@@ -2077,21 +2195,23 @@
       <c r="D54" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="7" t="str">
+        <f>_xlfn.CONCAT(B54,D54)</f>
         <v>URETA MENDOZA ERMEL RUBENLIQUIDO</v>
-      </c>
-      <c r="F54" s="8">
-        <v>100</v>
-      </c>
-      <c r="G54" s="8">
-        <v>100</v>
       </c>
       <c r="H54" s="8">
         <v>100</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I54" s="8">
+        <v>100</v>
+      </c>
+      <c r="J54" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>8</v>
       </c>
@@ -2104,21 +2224,23 @@
       <c r="D55" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E55" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="7" t="str">
+        <f>_xlfn.CONCAT(B55,D55)</f>
         <v>URETA MENDOZA ERMEL RUBENPOLVO DETERGENTE</v>
-      </c>
-      <c r="F55" s="8">
-        <v>698</v>
-      </c>
-      <c r="G55" s="8">
-        <v>698</v>
       </c>
       <c r="H55" s="8">
         <v>698</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I55" s="8">
+        <v>698</v>
+      </c>
+      <c r="J55" s="8">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>8</v>
       </c>
@@ -2131,21 +2253,23 @@
       <c r="D56" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E56" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="7" t="str">
+        <f>_xlfn.CONCAT(B56,D56)</f>
         <v>URETA MENDOZA ERMEL RUBENOTRAS CATEGORIAS</v>
       </c>
-      <c r="F56" s="8">
-        <v>10</v>
-      </c>
-      <c r="G56" s="8">
-        <v>10</v>
-      </c>
       <c r="H56" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I56" s="8">
+        <v>10</v>
+      </c>
+      <c r="J56" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>22</v>
       </c>
@@ -2158,21 +2282,23 @@
       <c r="D57" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7" t="str">
+        <f>_xlfn.CONCAT(B57,D57)</f>
         <v>TOALOMBO LLACA ROSA ISABELBARRA</v>
-      </c>
-      <c r="F57" s="8">
-        <v>3400</v>
-      </c>
-      <c r="G57" s="8">
-        <v>3400</v>
       </c>
       <c r="H57" s="8">
         <v>3400</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57" s="8">
+        <v>3400</v>
+      </c>
+      <c r="J57" s="8">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>22</v>
       </c>
@@ -2185,21 +2311,23 @@
       <c r="D58" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E58" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7" t="str">
+        <f>_xlfn.CONCAT(B58,D58)</f>
         <v>TOALOMBO LLACA ROSA ISABELCREMA</v>
-      </c>
-      <c r="F58" s="8">
-        <v>542</v>
-      </c>
-      <c r="G58" s="8">
-        <v>542</v>
       </c>
       <c r="H58" s="8">
         <v>542</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I58" s="8">
+        <v>542</v>
+      </c>
+      <c r="J58" s="8">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>22</v>
       </c>
@@ -2212,21 +2340,23 @@
       <c r="D59" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E59" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7" t="str">
+        <f>_xlfn.CONCAT(B59,D59)</f>
         <v>TOALOMBO LLACA ROSA ISABELLIQUIDO</v>
-      </c>
-      <c r="F59" s="8">
-        <v>40</v>
-      </c>
-      <c r="G59" s="8">
-        <v>40</v>
       </c>
       <c r="H59" s="8">
         <v>40</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59" s="8">
+        <v>40</v>
+      </c>
+      <c r="J59" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>22</v>
       </c>
@@ -2239,21 +2369,23 @@
       <c r="D60" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7" t="str">
+        <f>_xlfn.CONCAT(B60,D60)</f>
         <v>TOALOMBO LLACA ROSA ISABELPOLVO DETERGENTE</v>
-      </c>
-      <c r="F60" s="8">
-        <v>2105</v>
-      </c>
-      <c r="G60" s="8">
-        <v>2105</v>
       </c>
       <c r="H60" s="8">
         <v>2105</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I60" s="8">
+        <v>2105</v>
+      </c>
+      <c r="J60" s="8">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>22</v>
       </c>
@@ -2266,17 +2398,19 @@
       <c r="D61" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E61" s="7" t="str">
-        <f t="shared" si="0"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7" t="str">
+        <f>_xlfn.CONCAT(B61,D61)</f>
         <v>TOALOMBO LLACA ROSA ISABELOTRAS CATEGORIAS</v>
       </c>
-      <c r="F61" s="8">
+      <c r="H61" s="8">
         <v>20</v>
       </c>
-      <c r="G61" s="8">
+      <c r="I61" s="8">
         <v>20</v>
       </c>
-      <c r="H61" s="8">
+      <c r="J61" s="8">
         <v>20</v>
       </c>
     </row>

--- a/datos/repositorio prueba trimestral.xlsx
+++ b/datos/repositorio prueba trimestral.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\OneDrive\Desktop\trabajo\Trazabilidad_seguimiento\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8313660C-B41D-4C63-8E1A-5F521DBB75CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_1CEE0152576CA62EEF76E4345C5766F8A180CAD5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF28ABC6-9E45-43EC-AA8F-B480BA3DE30B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,15 +28,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="46">
   <si>
     <t>CEDI</t>
   </si>
@@ -53,6 +47,12 @@
     <t>CATEGORIAS</t>
   </si>
   <si>
+    <t>SUBCATEGORIA</t>
+  </si>
+  <si>
+    <t>MARCA</t>
+  </si>
+  <si>
     <t>CONCAT</t>
   </si>
   <si>
@@ -77,27 +77,57 @@
     <t>BARRA</t>
   </si>
   <si>
+    <t>LAVAVAJILLAS</t>
+  </si>
+  <si>
+    <t>EL ARRANCAGRASA</t>
+  </si>
+  <si>
     <t>CREMA</t>
   </si>
   <si>
+    <t>LAVA</t>
+  </si>
+  <si>
     <t>LIQUIDO</t>
   </si>
   <si>
+    <t>DESINFECTANTES</t>
+  </si>
+  <si>
+    <t>GOL</t>
+  </si>
+  <si>
     <t>ZAMBRANO ZAMBRANO CLEYTON ELIECERLIQUIDO</t>
   </si>
   <si>
     <t>POLVO DETERGENTE</t>
   </si>
   <si>
+    <t>DETERGENTE</t>
+  </si>
+  <si>
     <t>OTRAS CATEGORIAS</t>
   </si>
   <si>
     <t>ZAMBRANO VALENCIA MARGARITA</t>
   </si>
   <si>
+    <t>SAPOLIO</t>
+  </si>
+  <si>
     <t>ZAMBRANO MOLINA JORGE EDUARDO</t>
   </si>
   <si>
+    <t>ROPA</t>
+  </si>
+  <si>
+    <t>EL MACHO</t>
+  </si>
+  <si>
+    <t>CIERTO</t>
+  </si>
+  <si>
     <t>ZAMBRANO MACIAS FRANCISCO GREGORIO</t>
   </si>
   <si>
@@ -107,6 +137,12 @@
     <t>YUCAILLA PADILLA RENE WILFRIDO</t>
   </si>
   <si>
+    <t>JABON TOCADOR</t>
+  </si>
+  <si>
+    <t>MISTY</t>
+  </si>
+  <si>
     <t>XAVIER ALVARADO</t>
   </si>
   <si>
@@ -119,6 +155,9 @@
     <t>YAGUACHI QUISHPI MARIA ELVIRA</t>
   </si>
   <si>
+    <t>SUAVIZANTES</t>
+  </si>
+  <si>
     <t>WANG CHONG LONG</t>
   </si>
   <si>
@@ -132,12 +171,6 @@
   </si>
   <si>
     <t>TOALOMBO LLACA ROSA ISABEL</t>
-  </si>
-  <si>
-    <t>MARCA</t>
-  </si>
-  <si>
-    <t>SUBCATEGORIA</t>
   </si>
 </sst>
 </file>
@@ -272,7 +305,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -294,7 +327,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -635,7 +668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3898A9C6-98A7-4AA3-8BAF-4B75AC1084B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -663,39 +696,43 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="G2" s="7" t="str">
         <f>_xlfn.CONCAT(B2,D2)</f>
         <v>ZAMBRANO ZAMBRANO CLEYTON ELIECERBARRA</v>
@@ -712,19 +749,23 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G3" s="7" t="str">
         <f>_xlfn.CONCAT(B3,D3)</f>
         <v>ZAMBRANO ZAMBRANO CLEYTON ELIECERCREMA</v>
@@ -741,21 +782,25 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="G4" s="7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H4" s="8">
         <v>110</v>
@@ -769,21 +814,25 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+        <v>22</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="G5" s="7" t="str">
-        <f>_xlfn.CONCAT(B5,D5)</f>
+        <f t="shared" ref="G5:G36" si="0">_xlfn.CONCAT(B5,D5)</f>
         <v>ZAMBRANO ZAMBRANO CLEYTON ELIECERPOLVO DETERGENTE</v>
       </c>
       <c r="H5" s="8">
@@ -798,21 +847,21 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="str">
-        <f>_xlfn.CONCAT(B6,D6)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO ZAMBRANO CLEYTON ELIECEROTRAS CATEGORIAS</v>
       </c>
       <c r="H6" s="8">
@@ -827,21 +876,25 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
       <c r="G7" s="7" t="str">
-        <f>_xlfn.CONCAT(B7,D7)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO VALENCIA MARGARITABARRA</v>
       </c>
       <c r="H7" s="8">
@@ -856,21 +909,25 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
       <c r="G8" s="7" t="str">
-        <f>_xlfn.CONCAT(B8,D8)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO VALENCIA MARGARITACREMA</v>
       </c>
       <c r="H8" s="8">
@@ -885,21 +942,25 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
       <c r="G9" s="7" t="str">
-        <f>_xlfn.CONCAT(B9,D9)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO VALENCIA MARGARITALIQUIDO</v>
       </c>
       <c r="H9" s="8">
@@ -914,21 +975,25 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+        <v>22</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="G10" s="7" t="str">
-        <f>_xlfn.CONCAT(B10,D10)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO VALENCIA MARGARITAPOLVO DETERGENTE</v>
       </c>
       <c r="H10" s="8">
@@ -943,21 +1008,21 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7" t="str">
-        <f>_xlfn.CONCAT(B11,D11)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO VALENCIA MARGARITAOTRAS CATEGORIAS</v>
       </c>
       <c r="H11" s="8">
@@ -972,21 +1037,25 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="G12" s="7" t="str">
-        <f>_xlfn.CONCAT(B12,D12)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MOLINA JORGE EDUARDOBARRA</v>
       </c>
       <c r="H12" s="8">
@@ -1001,21 +1070,25 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G13" s="7" t="str">
-        <f>_xlfn.CONCAT(B13,D13)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MOLINA JORGE EDUARDOCREMA</v>
       </c>
       <c r="H13" s="8">
@@ -1030,21 +1103,25 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="G14" s="7" t="str">
-        <f>_xlfn.CONCAT(B14,D14)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MOLINA JORGE EDUARDOLIQUIDO</v>
       </c>
       <c r="H14" s="8">
@@ -1059,21 +1136,25 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+        <v>22</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="G15" s="7" t="str">
-        <f>_xlfn.CONCAT(B15,D15)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MOLINA JORGE EDUARDOPOLVO DETERGENTE</v>
       </c>
       <c r="H15" s="8">
@@ -1088,21 +1169,21 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7" t="str">
-        <f>_xlfn.CONCAT(B16,D16)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MOLINA JORGE EDUARDOOTRAS CATEGORIAS</v>
       </c>
       <c r="H16" s="8">
@@ -1117,21 +1198,25 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="G17" s="7" t="str">
-        <f>_xlfn.CONCAT(B17,D17)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOBARRA</v>
       </c>
       <c r="H17" s="8">
@@ -1146,21 +1231,25 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G18" s="7" t="str">
-        <f>_xlfn.CONCAT(B18,D18)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOCREMA</v>
       </c>
       <c r="H18" s="8">
@@ -1175,21 +1264,25 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="G19" s="7" t="str">
-        <f>_xlfn.CONCAT(B19,D19)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOLIQUIDO</v>
       </c>
       <c r="H19" s="8">
@@ -1204,21 +1297,25 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+        <v>22</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="G20" s="7" t="str">
-        <f>_xlfn.CONCAT(B20,D20)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOPOLVO DETERGENTE</v>
       </c>
       <c r="H20" s="8">
@@ -1233,21 +1330,21 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7" t="str">
-        <f>_xlfn.CONCAT(B21,D21)</f>
+        <f t="shared" si="0"/>
         <v>ZAMBRANO MACIAS FRANCISCO GREGORIOOTRAS CATEGORIAS</v>
       </c>
       <c r="H21" s="8">
@@ -1262,21 +1359,25 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G22" s="7" t="str">
-        <f>_xlfn.CONCAT(B22,D22)</f>
+        <f t="shared" si="0"/>
         <v>YUCAILLA PADILLA RENE WILFRIDOBARRA</v>
       </c>
       <c r="H22" s="9">
@@ -1291,21 +1392,25 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G23" s="7" t="str">
-        <f>_xlfn.CONCAT(B23,D23)</f>
+        <f t="shared" si="0"/>
         <v>YUCAILLA PADILLA RENE WILFRIDOCREMA</v>
       </c>
       <c r="H23" s="8">
@@ -1320,21 +1425,25 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="G24" s="7" t="str">
-        <f>_xlfn.CONCAT(B24,D24)</f>
+        <f t="shared" si="0"/>
         <v>YUCAILLA PADILLA RENE WILFRIDOLIQUIDO</v>
       </c>
       <c r="H24" s="8">
@@ -1349,21 +1458,25 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
       <c r="G25" s="7" t="str">
-        <f>_xlfn.CONCAT(B25,D25)</f>
+        <f t="shared" si="0"/>
         <v>YUCAILLA PADILLA RENE WILFRIDOPOLVO DETERGENTE</v>
       </c>
       <c r="H25" s="9">
@@ -1378,21 +1491,21 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7" t="str">
-        <f>_xlfn.CONCAT(B26,D26)</f>
+        <f t="shared" si="0"/>
         <v>YUCAILLA PADILLA RENE WILFRIDOOTRAS CATEGORIAS</v>
       </c>
       <c r="H26" s="8"/>
@@ -1401,21 +1514,25 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="G27" s="7" t="str">
-        <f>_xlfn.CONCAT(B27,D27)</f>
+        <f t="shared" si="0"/>
         <v>YANEZ CARDENAS ESTELA ELIZABETHBARRA</v>
       </c>
       <c r="H27" s="8">
@@ -1430,21 +1547,25 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G28" s="7" t="str">
-        <f>_xlfn.CONCAT(B28,D28)</f>
+        <f t="shared" si="0"/>
         <v>YANEZ CARDENAS ESTELA ELIZABETHCREMA</v>
       </c>
       <c r="H28" s="8">
@@ -1459,21 +1580,25 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G29" s="7" t="str">
-        <f>_xlfn.CONCAT(B29,D29)</f>
+        <f t="shared" si="0"/>
         <v>YANEZ CARDENAS ESTELA ELIZABETHLIQUIDO</v>
       </c>
       <c r="H29" s="8">
@@ -1488,21 +1613,25 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="E30" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="F30" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="G30" s="7" t="str">
-        <f>_xlfn.CONCAT(B30,D30)</f>
+        <f t="shared" si="0"/>
         <v>YANEZ CARDENAS ESTELA ELIZABETHPOLVO DETERGENTE</v>
       </c>
       <c r="H30" s="8">
@@ -1517,21 +1646,21 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7" t="str">
-        <f>_xlfn.CONCAT(B31,D31)</f>
+        <f t="shared" si="0"/>
         <v>YANEZ CARDENAS ESTELA ELIZABETHOTRAS CATEGORIAS</v>
       </c>
       <c r="H31" s="8">
@@ -1546,21 +1675,25 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="G32" s="7" t="str">
-        <f>_xlfn.CONCAT(B32,D32)</f>
+        <f t="shared" si="0"/>
         <v>YAGUACHI QUISHPI MARIA ELVIRABARRA</v>
       </c>
       <c r="H32" s="8">
@@ -1575,21 +1708,25 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G33" s="7" t="str">
-        <f>_xlfn.CONCAT(B33,D33)</f>
+        <f t="shared" si="0"/>
         <v>YAGUACHI QUISHPI MARIA ELVIRACREMA</v>
       </c>
       <c r="H33" s="8">
@@ -1604,21 +1741,25 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="G34" s="7" t="str">
-        <f>_xlfn.CONCAT(B34,D34)</f>
+        <f t="shared" si="0"/>
         <v>YAGUACHI QUISHPI MARIA ELVIRALIQUIDO</v>
       </c>
       <c r="H34" s="8">
@@ -1633,21 +1774,25 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
+      <c r="E35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="G35" s="7" t="str">
-        <f>_xlfn.CONCAT(B35,D35)</f>
+        <f t="shared" si="0"/>
         <v>YAGUACHI QUISHPI MARIA ELVIRAPOLVO DETERGENTE</v>
       </c>
       <c r="H35" s="8">
@@ -1662,21 +1807,21 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7" t="str">
-        <f>_xlfn.CONCAT(B36,D36)</f>
+        <f t="shared" si="0"/>
         <v>YAGUACHI QUISHPI MARIA ELVIRAOTRAS CATEGORIAS</v>
       </c>
       <c r="H36" s="8">
@@ -1691,21 +1836,25 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G37" s="7" t="str">
-        <f>_xlfn.CONCAT(B37,D37)</f>
+        <f t="shared" ref="G37:G61" si="1">_xlfn.CONCAT(B37,D37)</f>
         <v>WANG CHONG LONGBARRA</v>
       </c>
       <c r="H37" s="8">
@@ -1720,50 +1869,58 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G38" s="7" t="str">
-        <f>_xlfn.CONCAT(B38,D38)</f>
+        <f t="shared" si="1"/>
         <v>WANG CHONG LONGCREMA</v>
       </c>
       <c r="H38" s="8">
-        <v>1632.3400000000001</v>
+        <v>1632.34</v>
       </c>
       <c r="I38" s="8">
-        <v>1632.3400000000001</v>
+        <v>1632.34</v>
       </c>
       <c r="J38" s="8">
-        <v>1632.3400000000001</v>
+        <v>1632.34</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="G39" s="7" t="str">
-        <f>_xlfn.CONCAT(B39,D39)</f>
+        <f t="shared" si="1"/>
         <v>WANG CHONG LONGLIQUIDO</v>
       </c>
       <c r="H39" s="8">
@@ -1778,50 +1935,54 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
       <c r="G40" s="7" t="str">
-        <f>_xlfn.CONCAT(B40,D40)</f>
+        <f t="shared" si="1"/>
         <v>WANG CHONG LONGPOLVO DETERGENTE</v>
       </c>
       <c r="H40" s="8">
-        <v>1764.9399999999998</v>
+        <v>1764.94</v>
       </c>
       <c r="I40" s="8">
-        <v>1764.9399999999998</v>
+        <v>1764.94</v>
       </c>
       <c r="J40" s="8">
-        <v>1764.9399999999998</v>
+        <v>1764.94</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7" t="str">
-        <f>_xlfn.CONCAT(B41,D41)</f>
+        <f t="shared" si="1"/>
         <v>WANG CHONG LONGOTRAS CATEGORIAS</v>
       </c>
       <c r="H41" s="8">
@@ -1836,21 +1997,25 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="G42" s="7" t="str">
-        <f>_xlfn.CONCAT(B42,D42)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA YIMMY ANTONIOBARRA</v>
       </c>
       <c r="H42" s="8">
@@ -1865,21 +2030,25 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G43" s="7" t="str">
-        <f>_xlfn.CONCAT(B43,D43)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA YIMMY ANTONIOCREMA</v>
       </c>
       <c r="H43" s="8">
@@ -1894,21 +2063,25 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="G44" s="7" t="str">
-        <f>_xlfn.CONCAT(B44,D44)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA YIMMY ANTONIOLIQUIDO</v>
       </c>
       <c r="H44" s="8">
@@ -1923,21 +2096,25 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
+        <v>22</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="G45" s="7" t="str">
-        <f>_xlfn.CONCAT(B45,D45)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA YIMMY ANTONIOPOLVO DETERGENTE</v>
       </c>
       <c r="H45" s="8">
@@ -1952,21 +2129,21 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7" t="str">
-        <f>_xlfn.CONCAT(B46,D46)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA YIMMY ANTONIOOTRAS CATEGORIAS</v>
       </c>
       <c r="H46" s="8">
@@ -1981,21 +2158,25 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="G47" s="7" t="str">
-        <f>_xlfn.CONCAT(B47,D47)</f>
+        <f t="shared" si="1"/>
         <v>ROBERT - PONCE COMPANY S.A.SBARRA</v>
       </c>
       <c r="H47" s="8">
@@ -2010,21 +2191,25 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G48" s="7" t="str">
-        <f>_xlfn.CONCAT(B48,D48)</f>
+        <f t="shared" si="1"/>
         <v>ROBERT - PONCE COMPANY S.A.SCREMA</v>
       </c>
       <c r="H48" s="8">
@@ -2039,21 +2224,25 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G49" s="7" t="str">
-        <f>_xlfn.CONCAT(B49,D49)</f>
+        <f t="shared" si="1"/>
         <v>ROBERT - PONCE COMPANY S.A.SLIQUIDO</v>
       </c>
       <c r="H49" s="8">
@@ -2068,21 +2257,25 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
+        <v>22</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="G50" s="7" t="str">
-        <f>_xlfn.CONCAT(B50,D50)</f>
+        <f t="shared" si="1"/>
         <v>ROBERT - PONCE COMPANY S.A.SPOLVO DETERGENTE</v>
       </c>
       <c r="H50" s="8">
@@ -2097,21 +2290,21 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="7" t="str">
-        <f>_xlfn.CONCAT(B51,D51)</f>
+        <f t="shared" si="1"/>
         <v>ROBERT - PONCE COMPANY S.A.SOTRAS CATEGORIAS</v>
       </c>
       <c r="H51" s="8">
@@ -2126,21 +2319,25 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>17</v>
+      </c>
       <c r="G52" s="7" t="str">
-        <f>_xlfn.CONCAT(B52,D52)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA ERMEL RUBENBARRA</v>
       </c>
       <c r="H52" s="8">
@@ -2155,21 +2352,25 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>17</v>
+      </c>
       <c r="G53" s="7" t="str">
-        <f>_xlfn.CONCAT(B53,D53)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA ERMEL RUBENCREMA</v>
       </c>
       <c r="H53" s="8">
@@ -2184,21 +2385,25 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
+        <v>18</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="G54" s="7" t="str">
-        <f>_xlfn.CONCAT(B54,D54)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA ERMEL RUBENLIQUIDO</v>
       </c>
       <c r="H54" s="8">
@@ -2213,21 +2418,25 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
+        <v>22</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="G55" s="7" t="str">
-        <f>_xlfn.CONCAT(B55,D55)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA ERMEL RUBENPOLVO DETERGENTE</v>
       </c>
       <c r="H55" s="8">
@@ -2242,21 +2451,21 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="G56" s="7" t="str">
-        <f>_xlfn.CONCAT(B56,D56)</f>
+        <f t="shared" si="1"/>
         <v>URETA MENDOZA ERMEL RUBENOTRAS CATEGORIAS</v>
       </c>
       <c r="H56" s="8">
@@ -2271,21 +2480,25 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="G57" s="7" t="str">
-        <f>_xlfn.CONCAT(B57,D57)</f>
+        <f t="shared" si="1"/>
         <v>TOALOMBO LLACA ROSA ISABELBARRA</v>
       </c>
       <c r="H57" s="8">
@@ -2300,21 +2513,25 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G58" s="7" t="str">
-        <f>_xlfn.CONCAT(B58,D58)</f>
+        <f t="shared" si="1"/>
         <v>TOALOMBO LLACA ROSA ISABELCREMA</v>
       </c>
       <c r="H58" s="8">
@@ -2329,21 +2546,25 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="G59" s="7" t="str">
-        <f>_xlfn.CONCAT(B59,D59)</f>
+        <f t="shared" si="1"/>
         <v>TOALOMBO LLACA ROSA ISABELLIQUIDO</v>
       </c>
       <c r="H59" s="8">
@@ -2358,21 +2579,25 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B60" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
+      <c r="E60" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="G60" s="7" t="str">
-        <f>_xlfn.CONCAT(B60,D60)</f>
+        <f t="shared" si="1"/>
         <v>TOALOMBO LLACA ROSA ISABELPOLVO DETERGENTE</v>
       </c>
       <c r="H60" s="8">
@@ -2387,21 +2612,21 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C61" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
       <c r="G61" s="7" t="str">
-        <f>_xlfn.CONCAT(B61,D61)</f>
+        <f t="shared" si="1"/>
         <v>TOALOMBO LLACA ROSA ISABELOTRAS CATEGORIAS</v>
       </c>
       <c r="H61" s="8">
